--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136928012</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136928005</v>
       </c>
       <c r="B4" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136928012</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136928005</v>
       </c>
       <c r="B4" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -831,11 +831,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136928012</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136928005</v>
       </c>
       <c r="B4" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136928012</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136928005</v>
       </c>
       <c r="B4" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136928012</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136928005</v>
       </c>
       <c r="B4" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40219-2025 artfynd.xlsx
+++ b/artfynd/A 40219-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136928009</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
